--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_o_higgins.xlsx
@@ -362,42 +362,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>E_PRENETA_a</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>E_BASNETA_a</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>E_MEDIANETA_a</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>E_SUPNETA_a</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>E_PREBRUT_a</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>E_PRENETA_a</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>E_BASBRUT_a</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>E_BASNETA_a</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>E_MEDIABRUT_a</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>E_MEDIANETA_a</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>E_SUPBRUT_a</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>E_SUPNETA_a</t>
         </is>
       </c>
     </row>
@@ -408,28 +408,28 @@
         </is>
       </c>
       <c r="B2">
+        <v>55.67392</v>
+      </c>
+      <c r="C2">
+        <v>94.93595000000001</v>
+      </c>
+      <c r="D2">
+        <v>82.40246</v>
+      </c>
+      <c r="E2">
+        <v>42.49575</v>
+      </c>
+      <c r="F2">
         <v>56.07269</v>
       </c>
-      <c r="C2">
-        <v>55.67392</v>
-      </c>
-      <c r="D2">
+      <c r="G2">
         <v>99.97516</v>
       </c>
-      <c r="E2">
-        <v>94.93595000000001</v>
-      </c>
-      <c r="F2">
+      <c r="H2">
         <v>103.6379</v>
       </c>
-      <c r="G2">
-        <v>82.40246</v>
-      </c>
-      <c r="H2">
+      <c r="I2">
         <v>64.38871</v>
-      </c>
-      <c r="I2">
-        <v>42.49575</v>
       </c>
     </row>
     <row r="3">
@@ -439,28 +439,28 @@
         </is>
       </c>
       <c r="B3">
+        <v>59.34195</v>
+      </c>
+      <c r="C3">
+        <v>95.55556</v>
+      </c>
+      <c r="D3">
+        <v>86.08816</v>
+      </c>
+      <c r="E3">
+        <v>37.19912</v>
+      </c>
+      <c r="F3">
         <v>59.45946</v>
       </c>
-      <c r="C3">
-        <v>59.34195</v>
-      </c>
-      <c r="D3">
+      <c r="G3">
         <v>99.93056</v>
       </c>
-      <c r="E3">
-        <v>95.55556</v>
-      </c>
-      <c r="F3">
+      <c r="H3">
         <v>108.8154</v>
       </c>
-      <c r="G3">
-        <v>86.08816</v>
-      </c>
-      <c r="H3">
+      <c r="I3">
         <v>53.75638</v>
-      </c>
-      <c r="I3">
-        <v>37.19912</v>
       </c>
     </row>
     <row r="4">
@@ -470,28 +470,28 @@
         </is>
       </c>
       <c r="B4">
+        <v>57.05128</v>
+      </c>
+      <c r="C4">
+        <v>97.01897</v>
+      </c>
+      <c r="D4">
+        <v>85.50368</v>
+      </c>
+      <c r="E4">
+        <v>40.63745</v>
+      </c>
+      <c r="F4">
         <v>57.26496</v>
       </c>
-      <c r="C4">
-        <v>57.05128</v>
-      </c>
-      <c r="D4">
+      <c r="G4">
         <v>102.981</v>
       </c>
-      <c r="E4">
-        <v>97.01897</v>
-      </c>
-      <c r="F4">
+      <c r="H4">
         <v>102.457</v>
       </c>
-      <c r="G4">
-        <v>85.50368</v>
-      </c>
-      <c r="H4">
+      <c r="I4">
         <v>54.58167</v>
-      </c>
-      <c r="I4">
-        <v>40.63745</v>
       </c>
     </row>
     <row r="5">
@@ -501,28 +501,28 @@
         </is>
       </c>
       <c r="B5">
+        <v>54.57143</v>
+      </c>
+      <c r="C5">
+        <v>97.31664000000001</v>
+      </c>
+      <c r="D5">
+        <v>85.18182</v>
+      </c>
+      <c r="E5">
+        <v>34.45268</v>
+      </c>
+      <c r="F5">
         <v>55.07143</v>
       </c>
-      <c r="C5">
-        <v>54.57143</v>
-      </c>
-      <c r="D5">
+      <c r="G5">
         <v>102.9964</v>
       </c>
-      <c r="E5">
-        <v>97.31664000000001</v>
-      </c>
-      <c r="F5">
+      <c r="H5">
         <v>109.6364</v>
       </c>
-      <c r="G5">
-        <v>85.18182</v>
-      </c>
-      <c r="H5">
+      <c r="I5">
         <v>44.65765</v>
-      </c>
-      <c r="I5">
-        <v>34.45268</v>
       </c>
     </row>
     <row r="6">
@@ -532,28 +532,28 @@
         </is>
       </c>
       <c r="B6">
+        <v>61.01587</v>
+      </c>
+      <c r="C6">
+        <v>97.12032000000001</v>
+      </c>
+      <c r="D6">
+        <v>85.12138</v>
+      </c>
+      <c r="E6">
+        <v>40.47421</v>
+      </c>
+      <c r="F6">
         <v>61.33333</v>
       </c>
-      <c r="C6">
-        <v>61.01587</v>
-      </c>
-      <c r="D6">
+      <c r="G6">
         <v>101.8935</v>
       </c>
-      <c r="E6">
-        <v>97.12032000000001</v>
-      </c>
-      <c r="F6">
+      <c r="H6">
         <v>100.7048</v>
       </c>
-      <c r="G6">
-        <v>85.12138</v>
-      </c>
-      <c r="H6">
+      <c r="I6">
         <v>55.32446</v>
-      </c>
-      <c r="I6">
-        <v>40.47421</v>
       </c>
     </row>
     <row r="7">
@@ -563,28 +563,28 @@
         </is>
       </c>
       <c r="B7">
+        <v>56.0192</v>
+      </c>
+      <c r="C7">
+        <v>95.94069</v>
+      </c>
+      <c r="D7">
+        <v>82.37022</v>
+      </c>
+      <c r="E7">
+        <v>37.44305</v>
+      </c>
+      <c r="F7">
         <v>56.49926</v>
       </c>
-      <c r="C7">
-        <v>56.0192</v>
-      </c>
-      <c r="D7">
+      <c r="G7">
         <v>101.8474</v>
       </c>
-      <c r="E7">
-        <v>95.94069</v>
-      </c>
-      <c r="F7">
+      <c r="H7">
         <v>106.2684</v>
       </c>
-      <c r="G7">
-        <v>82.37022</v>
-      </c>
-      <c r="H7">
+      <c r="I7">
         <v>54.59662</v>
-      </c>
-      <c r="I7">
-        <v>37.44305</v>
       </c>
     </row>
     <row r="8">
@@ -594,28 +594,28 @@
         </is>
       </c>
       <c r="B8">
+        <v>59.17625</v>
+      </c>
+      <c r="C8">
+        <v>96.63545000000001</v>
+      </c>
+      <c r="D8">
+        <v>85.69364</v>
+      </c>
+      <c r="E8">
+        <v>34.46306</v>
+      </c>
+      <c r="F8">
         <v>59.35796</v>
       </c>
-      <c r="C8">
-        <v>59.17625</v>
-      </c>
-      <c r="D8">
+      <c r="G8">
         <v>102.7055</v>
       </c>
-      <c r="E8">
-        <v>96.63545000000001</v>
-      </c>
-      <c r="F8">
+      <c r="H8">
         <v>103.5405</v>
       </c>
-      <c r="G8">
-        <v>85.69364</v>
-      </c>
-      <c r="H8">
+      <c r="I8">
         <v>44.09749</v>
-      </c>
-      <c r="I8">
-        <v>34.46306</v>
       </c>
     </row>
     <row r="9">
@@ -625,28 +625,28 @@
         </is>
       </c>
       <c r="B9">
+        <v>52.12232</v>
+      </c>
+      <c r="C9">
+        <v>94.94978999999999</v>
+      </c>
+      <c r="D9">
+        <v>84.93789</v>
+      </c>
+      <c r="E9">
+        <v>52.35166</v>
+      </c>
+      <c r="F9">
         <v>52.80694</v>
       </c>
-      <c r="C9">
-        <v>52.12232</v>
-      </c>
-      <c r="D9">
+      <c r="G9">
         <v>98.93680000000001</v>
       </c>
-      <c r="E9">
-        <v>94.94978999999999</v>
-      </c>
-      <c r="F9">
+      <c r="H9">
         <v>100.6832</v>
       </c>
-      <c r="G9">
-        <v>84.93789</v>
-      </c>
-      <c r="H9">
+      <c r="I9">
         <v>75.78885</v>
-      </c>
-      <c r="I9">
-        <v>52.35166</v>
       </c>
     </row>
     <row r="10">
@@ -656,28 +656,28 @@
         </is>
       </c>
       <c r="B10">
+        <v>59.28571</v>
+      </c>
+      <c r="C10">
+        <v>96.66193</v>
+      </c>
+      <c r="D10">
+        <v>87.42331</v>
+      </c>
+      <c r="E10">
+        <v>33.61345</v>
+      </c>
+      <c r="F10">
         <v>59.52381</v>
       </c>
-      <c r="C10">
-        <v>59.28571</v>
-      </c>
-      <c r="D10">
+      <c r="G10">
         <v>100.071</v>
       </c>
-      <c r="E10">
-        <v>96.66193</v>
-      </c>
-      <c r="F10">
+      <c r="H10">
         <v>102.1472</v>
       </c>
-      <c r="G10">
-        <v>87.42331</v>
-      </c>
-      <c r="H10">
+      <c r="I10">
         <v>45.16807</v>
-      </c>
-      <c r="I10">
-        <v>33.61345</v>
       </c>
     </row>
     <row r="11">
@@ -687,28 +687,28 @@
         </is>
       </c>
       <c r="B11">
+        <v>62.11408</v>
+      </c>
+      <c r="C11">
+        <v>96.12551999999999</v>
+      </c>
+      <c r="D11">
+        <v>82.63433999999999</v>
+      </c>
+      <c r="E11">
+        <v>36.29004</v>
+      </c>
+      <c r="F11">
         <v>62.21873</v>
       </c>
-      <c r="C11">
-        <v>62.11408</v>
-      </c>
-      <c r="D11">
+      <c r="G11">
         <v>102.3055</v>
       </c>
-      <c r="E11">
-        <v>96.12551999999999</v>
-      </c>
-      <c r="F11">
+      <c r="H11">
         <v>107.536</v>
       </c>
-      <c r="G11">
-        <v>82.63433999999999</v>
-      </c>
-      <c r="H11">
+      <c r="I11">
         <v>51.31996</v>
-      </c>
-      <c r="I11">
-        <v>36.29004</v>
       </c>
     </row>
     <row r="12">
@@ -718,28 +718,28 @@
         </is>
       </c>
       <c r="B12">
+        <v>56.77291</v>
+      </c>
+      <c r="C12">
+        <v>96.07465000000001</v>
+      </c>
+      <c r="D12">
+        <v>84.05612000000001</v>
+      </c>
+      <c r="E12">
+        <v>41.33166</v>
+      </c>
+      <c r="F12">
         <v>57.47012</v>
       </c>
-      <c r="C12">
-        <v>56.77291</v>
-      </c>
-      <c r="D12">
+      <c r="G12">
         <v>101.5444</v>
       </c>
-      <c r="E12">
-        <v>96.07465000000001</v>
-      </c>
-      <c r="F12">
+      <c r="H12">
         <v>105.3571</v>
       </c>
-      <c r="G12">
-        <v>84.05612000000001</v>
-      </c>
-      <c r="H12">
+      <c r="I12">
         <v>54.77387</v>
-      </c>
-      <c r="I12">
-        <v>41.33166</v>
       </c>
     </row>
     <row r="13">
@@ -749,28 +749,28 @@
         </is>
       </c>
       <c r="B13">
+        <v>62.41611</v>
+      </c>
+      <c r="C13">
+        <v>97.00599</v>
+      </c>
+      <c r="D13">
+        <v>83.87943</v>
+      </c>
+      <c r="E13">
+        <v>34.96316</v>
+      </c>
+      <c r="F13">
         <v>63.08725</v>
       </c>
-      <c r="C13">
-        <v>62.41611</v>
-      </c>
-      <c r="D13">
+      <c r="G13">
         <v>103.3932</v>
       </c>
-      <c r="E13">
-        <v>97.00599</v>
-      </c>
-      <c r="F13">
+      <c r="H13">
         <v>106.8152</v>
       </c>
-      <c r="G13">
-        <v>83.87943</v>
-      </c>
-      <c r="H13">
+      <c r="I13">
         <v>49.69859</v>
-      </c>
-      <c r="I13">
-        <v>34.96316</v>
       </c>
     </row>
     <row r="14">
@@ -783,25 +783,25 @@
         <v>58.22994</v>
       </c>
       <c r="C14">
+        <v>96.82377</v>
+      </c>
+      <c r="D14">
+        <v>90.5232</v>
+      </c>
+      <c r="E14">
+        <v>36.24128</v>
+      </c>
+      <c r="F14">
         <v>58.22994</v>
       </c>
-      <c r="D14">
+      <c r="G14">
         <v>100.4611</v>
       </c>
-      <c r="E14">
-        <v>96.82377</v>
-      </c>
-      <c r="F14">
+      <c r="H14">
         <v>102.2705</v>
       </c>
-      <c r="G14">
-        <v>90.5232</v>
-      </c>
-      <c r="H14">
+      <c r="I14">
         <v>46.06181</v>
-      </c>
-      <c r="I14">
-        <v>36.24128</v>
       </c>
     </row>
     <row r="15">
@@ -811,28 +811,28 @@
         </is>
       </c>
       <c r="B15">
+        <v>63.76307</v>
+      </c>
+      <c r="C15">
+        <v>97.32659</v>
+      </c>
+      <c r="D15">
+        <v>89.23706</v>
+      </c>
+      <c r="E15">
+        <v>41.48199</v>
+      </c>
+      <c r="F15">
         <v>64.11150000000001</v>
       </c>
-      <c r="C15">
-        <v>63.76307</v>
-      </c>
-      <c r="D15">
+      <c r="G15">
         <v>101.1561</v>
       </c>
-      <c r="E15">
-        <v>97.32659</v>
-      </c>
-      <c r="F15">
+      <c r="H15">
         <v>104.4959</v>
       </c>
-      <c r="G15">
-        <v>89.23706</v>
-      </c>
-      <c r="H15">
+      <c r="I15">
         <v>54.01662</v>
-      </c>
-      <c r="I15">
-        <v>41.48199</v>
       </c>
     </row>
     <row r="16">
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="B16">
+        <v>59.99044</v>
+      </c>
+      <c r="C16">
+        <v>96.42803000000001</v>
+      </c>
+      <c r="D16">
+        <v>85.41177</v>
+      </c>
+      <c r="E16">
+        <v>37.91598</v>
+      </c>
+      <c r="F16">
         <v>60.30115</v>
       </c>
-      <c r="C16">
-        <v>59.99044</v>
-      </c>
-      <c r="D16">
+      <c r="G16">
         <v>101.266</v>
       </c>
-      <c r="E16">
-        <v>96.42803000000001</v>
-      </c>
-      <c r="F16">
+      <c r="H16">
         <v>107.4412</v>
       </c>
-      <c r="G16">
-        <v>85.41177</v>
-      </c>
-      <c r="H16">
+      <c r="I16">
         <v>55.23265</v>
-      </c>
-      <c r="I16">
-        <v>37.91598</v>
       </c>
     </row>
     <row r="17">
@@ -873,28 +873,28 @@
         </is>
       </c>
       <c r="B17">
+        <v>60.03889</v>
+      </c>
+      <c r="C17">
+        <v>96.13827999999999</v>
+      </c>
+      <c r="D17">
+        <v>85.6084</v>
+      </c>
+      <c r="E17">
+        <v>39.74715</v>
+      </c>
+      <c r="F17">
         <v>60.62226</v>
       </c>
-      <c r="C17">
-        <v>60.03889</v>
-      </c>
-      <c r="D17">
+      <c r="G17">
         <v>100.8097</v>
       </c>
-      <c r="E17">
-        <v>96.13827999999999</v>
-      </c>
-      <c r="F17">
+      <c r="H17">
         <v>104.509</v>
       </c>
-      <c r="G17">
-        <v>85.6084</v>
-      </c>
-      <c r="H17">
+      <c r="I17">
         <v>52.45144</v>
-      </c>
-      <c r="I17">
-        <v>39.74715</v>
       </c>
     </row>
     <row r="18">
@@ -904,28 +904,28 @@
         </is>
       </c>
       <c r="B18">
+        <v>59.57167</v>
+      </c>
+      <c r="C18">
+        <v>96.79259999999999</v>
+      </c>
+      <c r="D18">
+        <v>86.49805000000001</v>
+      </c>
+      <c r="E18">
+        <v>43.23055</v>
+      </c>
+      <c r="F18">
         <v>59.90115</v>
       </c>
-      <c r="C18">
-        <v>59.57167</v>
-      </c>
-      <c r="D18">
+      <c r="G18">
         <v>101.22</v>
       </c>
-      <c r="E18">
-        <v>96.79259999999999</v>
-      </c>
-      <c r="F18">
+      <c r="H18">
         <v>103.7743</v>
       </c>
-      <c r="G18">
-        <v>86.49805000000001</v>
-      </c>
-      <c r="H18">
+      <c r="I18">
         <v>57.62712</v>
-      </c>
-      <c r="I18">
-        <v>43.23055</v>
       </c>
     </row>
     <row r="19">
@@ -935,28 +935,28 @@
         </is>
       </c>
       <c r="B19">
+        <v>52.95056</v>
+      </c>
+      <c r="C19">
+        <v>94.11765</v>
+      </c>
+      <c r="D19">
+        <v>82.01663000000001</v>
+      </c>
+      <c r="E19">
+        <v>38.92617</v>
+      </c>
+      <c r="F19">
         <v>53.0303</v>
       </c>
-      <c r="C19">
-        <v>52.95056</v>
-      </c>
-      <c r="D19">
+      <c r="G19">
         <v>97.70308</v>
       </c>
-      <c r="E19">
-        <v>94.11765</v>
-      </c>
-      <c r="F19">
+      <c r="H19">
         <v>100.4158</v>
       </c>
-      <c r="G19">
-        <v>82.01663000000001</v>
-      </c>
-      <c r="H19">
+      <c r="I19">
         <v>53.02013</v>
-      </c>
-      <c r="I19">
-        <v>38.92617</v>
       </c>
     </row>
     <row r="20">
@@ -966,28 +966,28 @@
         </is>
       </c>
       <c r="B20">
+        <v>61.04651</v>
+      </c>
+      <c r="C20">
+        <v>97.10611</v>
+      </c>
+      <c r="D20">
+        <v>90.19607999999999</v>
+      </c>
+      <c r="E20">
+        <v>41.63701</v>
+      </c>
+      <c r="F20">
         <v>61.62791</v>
       </c>
-      <c r="C20">
-        <v>61.04651</v>
-      </c>
-      <c r="D20">
+      <c r="G20">
         <v>100</v>
       </c>
-      <c r="E20">
-        <v>97.10611</v>
-      </c>
-      <c r="F20">
+      <c r="H20">
         <v>99.34641000000001</v>
       </c>
-      <c r="G20">
-        <v>90.19607999999999</v>
-      </c>
-      <c r="H20">
+      <c r="I20">
         <v>57.65125</v>
-      </c>
-      <c r="I20">
-        <v>41.63701</v>
       </c>
     </row>
     <row r="21">
@@ -997,28 +997,28 @@
         </is>
       </c>
       <c r="B21">
+        <v>53.89909</v>
+      </c>
+      <c r="C21">
+        <v>97.14693</v>
+      </c>
+      <c r="D21">
+        <v>82.08092000000001</v>
+      </c>
+      <c r="E21">
+        <v>37.14286</v>
+      </c>
+      <c r="F21">
         <v>53.89908</v>
       </c>
-      <c r="C21">
-        <v>53.89909</v>
-      </c>
-      <c r="D21">
+      <c r="G21">
         <v>102.4251</v>
       </c>
-      <c r="E21">
-        <v>97.14693</v>
-      </c>
-      <c r="F21">
+      <c r="H21">
         <v>98.2659</v>
       </c>
-      <c r="G21">
-        <v>82.08092000000001</v>
-      </c>
-      <c r="H21">
+      <c r="I21">
         <v>48.57143</v>
-      </c>
-      <c r="I21">
-        <v>37.14286</v>
       </c>
     </row>
     <row r="22">
@@ -1031,25 +1031,25 @@
         <v>65.10538</v>
       </c>
       <c r="C22">
+        <v>96.33758</v>
+      </c>
+      <c r="D22">
+        <v>88.38863000000001</v>
+      </c>
+      <c r="E22">
+        <v>39.5189</v>
+      </c>
+      <c r="F22">
         <v>65.10538</v>
       </c>
-      <c r="D22">
+      <c r="G22">
         <v>100.9554</v>
       </c>
-      <c r="E22">
-        <v>96.33758</v>
-      </c>
-      <c r="F22">
+      <c r="H22">
         <v>100.237</v>
       </c>
-      <c r="G22">
-        <v>88.38863000000001</v>
-      </c>
-      <c r="H22">
+      <c r="I22">
         <v>50.28637</v>
-      </c>
-      <c r="I22">
-        <v>39.5189</v>
       </c>
     </row>
     <row r="23">
@@ -1062,25 +1062,25 @@
         <v>57.34072</v>
       </c>
       <c r="C23">
+        <v>93.98998</v>
+      </c>
+      <c r="D23">
+        <v>74.72924</v>
+      </c>
+      <c r="E23">
+        <v>34.30354</v>
+      </c>
+      <c r="F23">
         <v>57.34072</v>
       </c>
-      <c r="D23">
+      <c r="G23">
         <v>99.66611</v>
       </c>
-      <c r="E23">
-        <v>93.98998</v>
-      </c>
-      <c r="F23">
+      <c r="H23">
         <v>97.83394</v>
       </c>
-      <c r="G23">
-        <v>74.72924</v>
-      </c>
-      <c r="H23">
+      <c r="I23">
         <v>42.61954</v>
-      </c>
-      <c r="I23">
-        <v>34.30354</v>
       </c>
     </row>
     <row r="24">
@@ -1093,25 +1093,25 @@
         <v>49.83607</v>
       </c>
       <c r="C24">
+        <v>97.16446999999999</v>
+      </c>
+      <c r="D24">
+        <v>86.24160999999999</v>
+      </c>
+      <c r="E24">
+        <v>37.04189</v>
+      </c>
+      <c r="F24">
         <v>49.83607</v>
       </c>
-      <c r="D24">
+      <c r="G24">
         <v>102.0794</v>
       </c>
-      <c r="E24">
-        <v>97.16446999999999</v>
-      </c>
-      <c r="F24">
+      <c r="H24">
         <v>104.3624</v>
       </c>
-      <c r="G24">
-        <v>86.24160999999999</v>
-      </c>
-      <c r="H24">
+      <c r="I24">
         <v>44.37173</v>
-      </c>
-      <c r="I24">
-        <v>37.04189</v>
       </c>
     </row>
     <row r="25">
@@ -1121,28 +1121,28 @@
         </is>
       </c>
       <c r="B25">
+        <v>63.80502</v>
+      </c>
+      <c r="C25">
+        <v>95.61691999999999</v>
+      </c>
+      <c r="D25">
+        <v>81.6943</v>
+      </c>
+      <c r="E25">
+        <v>39.28257</v>
+      </c>
+      <c r="F25">
         <v>64.16025999999999</v>
       </c>
-      <c r="C25">
-        <v>63.80502</v>
-      </c>
-      <c r="D25">
+      <c r="G25">
         <v>100.9166</v>
       </c>
-      <c r="E25">
-        <v>95.61691999999999</v>
-      </c>
-      <c r="F25">
+      <c r="H25">
         <v>107.2224</v>
       </c>
-      <c r="G25">
-        <v>81.6943</v>
-      </c>
-      <c r="H25">
+      <c r="I25">
         <v>54.64349</v>
-      </c>
-      <c r="I25">
-        <v>39.28257</v>
       </c>
     </row>
     <row r="26">
@@ -1152,28 +1152,28 @@
         </is>
       </c>
       <c r="B26">
+        <v>61.3</v>
+      </c>
+      <c r="C26">
+        <v>96.26345999999999</v>
+      </c>
+      <c r="D26">
+        <v>89.38619</v>
+      </c>
+      <c r="E26">
+        <v>37.63757</v>
+      </c>
+      <c r="F26">
         <v>62</v>
       </c>
-      <c r="C26">
-        <v>61.3</v>
-      </c>
-      <c r="D26">
+      <c r="G26">
         <v>101.9633</v>
       </c>
-      <c r="E26">
-        <v>96.26345999999999</v>
-      </c>
-      <c r="F26">
+      <c r="H26">
         <v>106.3939</v>
       </c>
-      <c r="G26">
-        <v>89.38619</v>
-      </c>
-      <c r="H26">
+      <c r="I26">
         <v>51.87087</v>
-      </c>
-      <c r="I26">
-        <v>37.63757</v>
       </c>
     </row>
     <row r="27">
@@ -1183,28 +1183,28 @@
         </is>
       </c>
       <c r="B27">
+        <v>58.5556</v>
+      </c>
+      <c r="C27">
+        <v>96.46718</v>
+      </c>
+      <c r="D27">
+        <v>84.38735</v>
+      </c>
+      <c r="E27">
+        <v>35.17817</v>
+      </c>
+      <c r="F27">
         <v>58.96594</v>
       </c>
-      <c r="C27">
-        <v>58.5556</v>
-      </c>
-      <c r="D27">
+      <c r="G27">
         <v>101.5291</v>
       </c>
-      <c r="E27">
-        <v>96.46718</v>
-      </c>
-      <c r="F27">
+      <c r="H27">
         <v>109.2391</v>
       </c>
-      <c r="G27">
-        <v>84.38735</v>
-      </c>
-      <c r="H27">
+      <c r="I27">
         <v>47.66237</v>
-      </c>
-      <c r="I27">
-        <v>35.17817</v>
       </c>
     </row>
     <row r="28">
@@ -1217,25 +1217,25 @@
         <v>57.18157</v>
       </c>
       <c r="C28">
+        <v>96.42325</v>
+      </c>
+      <c r="D28">
+        <v>87.03704</v>
+      </c>
+      <c r="E28">
+        <v>39.25926</v>
+      </c>
+      <c r="F28">
         <v>57.18157</v>
       </c>
-      <c r="D28">
+      <c r="G28">
         <v>101.0432</v>
       </c>
-      <c r="E28">
-        <v>96.42325</v>
-      </c>
-      <c r="F28">
+      <c r="H28">
         <v>100.9259</v>
       </c>
-      <c r="G28">
-        <v>87.03704</v>
-      </c>
-      <c r="H28">
+      <c r="I28">
         <v>47.85185</v>
-      </c>
-      <c r="I28">
-        <v>39.25926</v>
       </c>
     </row>
     <row r="29">
@@ -1248,25 +1248,25 @@
         <v>56.54008</v>
       </c>
       <c r="C29">
+        <v>95.83767</v>
+      </c>
+      <c r="D29">
+        <v>89.65152999999999</v>
+      </c>
+      <c r="E29">
+        <v>35.15958</v>
+      </c>
+      <c r="F29">
         <v>56.54008</v>
       </c>
-      <c r="D29">
+      <c r="G29">
         <v>99.6358</v>
       </c>
-      <c r="E29">
-        <v>95.83767</v>
-      </c>
-      <c r="F29">
+      <c r="H29">
         <v>106.4414</v>
       </c>
-      <c r="G29">
-        <v>89.65152999999999</v>
-      </c>
-      <c r="H29">
+      <c r="I29">
         <v>48.51064</v>
-      </c>
-      <c r="I29">
-        <v>35.15958</v>
       </c>
     </row>
     <row r="30">
@@ -1275,23 +1275,23 @@
           <t>Palmilla</t>
         </is>
       </c>
+      <c r="C30">
+        <v>96.81698</v>
+      </c>
       <c r="D30">
+        <v>84.85915</v>
+      </c>
+      <c r="E30">
+        <v>34.9162</v>
+      </c>
+      <c r="G30">
         <v>101.7683</v>
       </c>
-      <c r="E30">
-        <v>96.81698</v>
-      </c>
-      <c r="F30">
+      <c r="H30">
         <v>102.8169</v>
       </c>
-      <c r="G30">
-        <v>84.85915</v>
-      </c>
-      <c r="H30">
+      <c r="I30">
         <v>46.74115</v>
-      </c>
-      <c r="I30">
-        <v>34.9162</v>
       </c>
     </row>
     <row r="31">
@@ -1304,25 +1304,25 @@
         <v>62.91391</v>
       </c>
       <c r="C31">
+        <v>96.41898</v>
+      </c>
+      <c r="D31">
+        <v>87.91540999999999</v>
+      </c>
+      <c r="E31">
+        <v>40.78014</v>
+      </c>
+      <c r="F31">
         <v>62.91391</v>
       </c>
-      <c r="D31">
+      <c r="G31">
         <v>101.1638</v>
       </c>
-      <c r="E31">
-        <v>96.41898</v>
-      </c>
-      <c r="F31">
+      <c r="H31">
         <v>96.97884999999999</v>
       </c>
-      <c r="G31">
-        <v>87.91540999999999</v>
-      </c>
-      <c r="H31">
+      <c r="I31">
         <v>56.91489</v>
-      </c>
-      <c r="I31">
-        <v>40.78014</v>
       </c>
     </row>
     <row r="32">
@@ -1332,28 +1332,28 @@
         </is>
       </c>
       <c r="B32">
+        <v>56.55878</v>
+      </c>
+      <c r="C32">
+        <v>96.24854000000001</v>
+      </c>
+      <c r="D32">
+        <v>84.89796</v>
+      </c>
+      <c r="E32">
+        <v>33.95639</v>
+      </c>
+      <c r="F32">
         <v>56.72913</v>
       </c>
-      <c r="C32">
-        <v>56.55878</v>
-      </c>
-      <c r="D32">
+      <c r="G32">
         <v>101.1723</v>
       </c>
-      <c r="E32">
-        <v>96.24854000000001</v>
-      </c>
-      <c r="F32">
+      <c r="H32">
         <v>107.1429</v>
       </c>
-      <c r="G32">
-        <v>84.89796</v>
-      </c>
-      <c r="H32">
+      <c r="I32">
         <v>48.18276</v>
-      </c>
-      <c r="I32">
-        <v>33.95639</v>
       </c>
     </row>
     <row r="33">
@@ -1366,25 +1366,25 @@
         <v>53.10735</v>
       </c>
       <c r="C33">
+        <v>98.02631</v>
+      </c>
+      <c r="D33">
+        <v>90.54053999999999</v>
+      </c>
+      <c r="E33">
+        <v>38.4127</v>
+      </c>
+      <c r="F33">
         <v>53.10735</v>
       </c>
-      <c r="D33">
+      <c r="G33">
         <v>100</v>
       </c>
-      <c r="E33">
-        <v>98.02631</v>
-      </c>
-      <c r="F33">
+      <c r="H33">
         <v>101.3513</v>
       </c>
-      <c r="G33">
-        <v>90.54053999999999</v>
-      </c>
-      <c r="H33">
+      <c r="I33">
         <v>49.52381</v>
-      </c>
-      <c r="I33">
-        <v>38.4127</v>
       </c>
     </row>
     <row r="34">
@@ -1394,28 +1394,28 @@
         </is>
       </c>
       <c r="B34">
+        <v>66.05947999999999</v>
+      </c>
+      <c r="C34">
+        <v>95.7505</v>
+      </c>
+      <c r="D34">
+        <v>86.81688</v>
+      </c>
+      <c r="E34">
+        <v>38.38114</v>
+      </c>
+      <c r="F34">
         <v>66.17101</v>
       </c>
-      <c r="C34">
-        <v>66.05947999999999</v>
-      </c>
-      <c r="D34">
+      <c r="G34">
         <v>100.6958</v>
       </c>
-      <c r="E34">
-        <v>95.7505</v>
-      </c>
-      <c r="F34">
+      <c r="H34">
         <v>105.6088</v>
       </c>
-      <c r="G34">
-        <v>86.81688</v>
-      </c>
-      <c r="H34">
+      <c r="I34">
         <v>52.28488</v>
-      </c>
-      <c r="I34">
-        <v>38.38114</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 19:47</t>
+    <t xml:space="preserve">2026-08-02 19:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 19:43</t>
+    <t xml:space="preserve">2026-08-05 10:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:36</t>
+    <t xml:space="preserve">2026-08-16 09:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 09:48</t>
+    <t xml:space="preserve">2026-08-19 12:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 12:01</t>
+    <t xml:space="preserve">2026-08-28 11:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:27</t>
+    <t xml:space="preserve">2026-09-06 17:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
